--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1199</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2334">
   <si>
     <t>en</t>
   </si>
@@ -5659,6 +5659,18 @@
     <t>舒尔克</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>《Sift》（灵感之作）</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift（香草味）</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -6562,6 +6574,12 @@
     <t>超杀</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
+    <t>《赛马娘》</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -6848,6 +6866,12 @@
   </si>
   <si>
     <t>冬天</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>冬季新品</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -7341,7 +7365,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1195"/>
+  <dimension ref="A1:B1199"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15177,36 +15201,36 @@
         <v>1912</v>
       </c>
       <c r="B979" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B980" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B981" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B982" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B983" t="s">
         <v>1919</v>
@@ -15321,23 +15345,23 @@
         <v>1946</v>
       </c>
       <c r="B997" t="s">
-        <v>1941</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B998" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="B999" t="s">
-        <v>1950</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
@@ -15441,23 +15465,23 @@
         <v>1975</v>
       </c>
       <c r="B1012" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B1013" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B1014" t="s">
         <v>1978</v>
-      </c>
-      <c r="B1014" t="s">
-        <v>1979</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
@@ -15489,23 +15513,23 @@
         <v>1986</v>
       </c>
       <c r="B1018" t="s">
-        <v>257</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B1019" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1020" t="s">
-        <v>1990</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
@@ -15593,20 +15617,20 @@
         <v>2011</v>
       </c>
       <c r="B1031" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B1032" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1033" t="s">
         <v>2015</v>
@@ -15673,20 +15697,20 @@
         <v>2030</v>
       </c>
       <c r="B1041" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B1042" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B1043" t="s">
         <v>2034</v>
@@ -16121,23 +16145,23 @@
         <v>2141</v>
       </c>
       <c r="B1097" t="s">
-        <v>531</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="B1098" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="B1099" t="s">
-        <v>2145</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
@@ -16201,23 +16225,23 @@
         <v>2160</v>
       </c>
       <c r="B1107" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="B1108" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B1109" t="s">
         <v>2163</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>2164</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
@@ -16345,44 +16369,44 @@
         <v>2195</v>
       </c>
       <c r="B1125" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="B1126" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="B1127" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="B1128" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B1129" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B1130" t="s">
         <v>2204</v>
@@ -16561,28 +16585,28 @@
         <v>2247</v>
       </c>
       <c r="B1152" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="B1153" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="B1154" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="B1155" t="s">
         <v>2252</v>
@@ -16590,23 +16614,23 @@
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="B1156" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="B1157" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="B1158" t="s">
         <v>2258</v>
@@ -16737,108 +16761,108 @@
         <v>2289</v>
       </c>
       <c r="B1174" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="B1175" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="B1176" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="B1177" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
       <c r="B1178" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="B1179" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="B1180" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="B1181" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="B1182" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="B1183" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="B1184" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="B1185" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="B1186" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="B1187" t="s">
         <v>2311</v>
@@ -16873,43 +16897,75 @@
         <v>2318</v>
       </c>
       <c r="B1191" t="s">
-        <v>68</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="B1192" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="B1193" t="s">
-        <v>2180</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="B1194" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="B1195" t="s">
-        <v>2325</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>2329</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>2330</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:2">
+      <c r="A1199" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>2333</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1195"/>
+  <autoFilter ref="A1:B1199"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
